--- a/data/nzd0150/nzd0150.xlsx
+++ b/data/nzd0150/nzd0150.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD307"/>
+  <dimension ref="A1:AD311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29677,7 +29677,7 @@
         <v>408.96</v>
       </c>
       <c r="C307" t="n">
-        <v>418.88</v>
+        <v>391.72</v>
       </c>
       <c r="D307" t="n">
         <v>390.58</v>
@@ -29758,6 +29758,390 @@
         <v>367.11</v>
       </c>
       <c r="AD307" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B308" t="n">
+        <v>412.85</v>
+      </c>
+      <c r="C308" t="n">
+        <v>396.95</v>
+      </c>
+      <c r="D308" t="n">
+        <v>394.77</v>
+      </c>
+      <c r="E308" t="n">
+        <v>381.05</v>
+      </c>
+      <c r="F308" t="n">
+        <v>381.06</v>
+      </c>
+      <c r="G308" t="n">
+        <v>382.91</v>
+      </c>
+      <c r="H308" t="n">
+        <v>374.17</v>
+      </c>
+      <c r="I308" t="n">
+        <v>365.26</v>
+      </c>
+      <c r="J308" t="n">
+        <v>354.06</v>
+      </c>
+      <c r="K308" t="n">
+        <v>352.36</v>
+      </c>
+      <c r="L308" t="n">
+        <v>351.35</v>
+      </c>
+      <c r="M308" t="n">
+        <v>349.68</v>
+      </c>
+      <c r="N308" t="n">
+        <v>351.27</v>
+      </c>
+      <c r="O308" t="n">
+        <v>353.14</v>
+      </c>
+      <c r="P308" t="n">
+        <v>357.5</v>
+      </c>
+      <c r="Q308" t="n">
+        <v>360.16</v>
+      </c>
+      <c r="R308" t="n">
+        <v>357.87</v>
+      </c>
+      <c r="S308" t="n">
+        <v>358.63</v>
+      </c>
+      <c r="T308" t="n">
+        <v>363.81</v>
+      </c>
+      <c r="U308" t="n">
+        <v>367.3</v>
+      </c>
+      <c r="V308" t="n">
+        <v>354.38</v>
+      </c>
+      <c r="W308" t="n">
+        <v>358.8</v>
+      </c>
+      <c r="X308" t="n">
+        <v>364.81</v>
+      </c>
+      <c r="Y308" t="n">
+        <v>371.69</v>
+      </c>
+      <c r="Z308" t="n">
+        <v>354.28</v>
+      </c>
+      <c r="AA308" t="n">
+        <v>348.27</v>
+      </c>
+      <c r="AB308" t="n">
+        <v>359.96</v>
+      </c>
+      <c r="AC308" t="n">
+        <v>367.11</v>
+      </c>
+      <c r="AD308" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>408.76</v>
+      </c>
+      <c r="C309" t="n">
+        <v>400.4</v>
+      </c>
+      <c r="D309" t="n">
+        <v>390.22</v>
+      </c>
+      <c r="E309" t="n">
+        <v>377.92</v>
+      </c>
+      <c r="F309" t="n">
+        <v>381.66</v>
+      </c>
+      <c r="G309" t="n">
+        <v>383.2</v>
+      </c>
+      <c r="H309" t="n">
+        <v>371.93</v>
+      </c>
+      <c r="I309" t="n">
+        <v>362.35</v>
+      </c>
+      <c r="J309" t="n">
+        <v>351.08</v>
+      </c>
+      <c r="K309" t="n">
+        <v>350.2</v>
+      </c>
+      <c r="L309" t="n">
+        <v>349.13</v>
+      </c>
+      <c r="M309" t="n">
+        <v>348.96</v>
+      </c>
+      <c r="N309" t="n">
+        <v>351.01</v>
+      </c>
+      <c r="O309" t="n">
+        <v>353.77</v>
+      </c>
+      <c r="P309" t="n">
+        <v>359.27</v>
+      </c>
+      <c r="Q309" t="n">
+        <v>360.27</v>
+      </c>
+      <c r="R309" t="n">
+        <v>357.91</v>
+      </c>
+      <c r="S309" t="n">
+        <v>357.83</v>
+      </c>
+      <c r="T309" t="n">
+        <v>363.71</v>
+      </c>
+      <c r="U309" t="n">
+        <v>367.04</v>
+      </c>
+      <c r="V309" t="n">
+        <v>354.38</v>
+      </c>
+      <c r="W309" t="n">
+        <v>358.61</v>
+      </c>
+      <c r="X309" t="n">
+        <v>360.58</v>
+      </c>
+      <c r="Y309" t="n">
+        <v>370.81</v>
+      </c>
+      <c r="Z309" t="n">
+        <v>355.75</v>
+      </c>
+      <c r="AA309" t="n">
+        <v>348.65</v>
+      </c>
+      <c r="AB309" t="n">
+        <v>360.75</v>
+      </c>
+      <c r="AC309" t="n">
+        <v>368.48</v>
+      </c>
+      <c r="AD309" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B310" t="n">
+        <v>410.42</v>
+      </c>
+      <c r="C310" t="n">
+        <v>403.41</v>
+      </c>
+      <c r="D310" t="n">
+        <v>393.17</v>
+      </c>
+      <c r="E310" t="n">
+        <v>380.48</v>
+      </c>
+      <c r="F310" t="n">
+        <v>381.86</v>
+      </c>
+      <c r="G310" t="n">
+        <v>383.5</v>
+      </c>
+      <c r="H310" t="n">
+        <v>372.71</v>
+      </c>
+      <c r="I310" t="n">
+        <v>364.01</v>
+      </c>
+      <c r="J310" t="n">
+        <v>352.3</v>
+      </c>
+      <c r="K310" t="n">
+        <v>351.12</v>
+      </c>
+      <c r="L310" t="n">
+        <v>350.74</v>
+      </c>
+      <c r="M310" t="n">
+        <v>349.55</v>
+      </c>
+      <c r="N310" t="n">
+        <v>351.4</v>
+      </c>
+      <c r="O310" t="n">
+        <v>353.99</v>
+      </c>
+      <c r="P310" t="n">
+        <v>359.23</v>
+      </c>
+      <c r="Q310" t="n">
+        <v>360.58</v>
+      </c>
+      <c r="R310" t="n">
+        <v>358.01</v>
+      </c>
+      <c r="S310" t="n">
+        <v>358.73</v>
+      </c>
+      <c r="T310" t="n">
+        <v>363.81</v>
+      </c>
+      <c r="U310" t="n">
+        <v>366.64</v>
+      </c>
+      <c r="V310" t="n">
+        <v>355.23</v>
+      </c>
+      <c r="W310" t="n">
+        <v>359.15</v>
+      </c>
+      <c r="X310" t="n">
+        <v>361.4</v>
+      </c>
+      <c r="Y310" t="n">
+        <v>371.38</v>
+      </c>
+      <c r="Z310" t="n">
+        <v>356.45</v>
+      </c>
+      <c r="AA310" t="n">
+        <v>349.31</v>
+      </c>
+      <c r="AB310" t="n">
+        <v>360.94</v>
+      </c>
+      <c r="AC310" t="n">
+        <v>369.3</v>
+      </c>
+      <c r="AD310" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:48+00:00</t>
+        </is>
+      </c>
+      <c r="B311" t="n">
+        <v>408.91</v>
+      </c>
+      <c r="C311" t="n">
+        <v>401.94</v>
+      </c>
+      <c r="D311" t="n">
+        <v>388.88</v>
+      </c>
+      <c r="E311" t="n">
+        <v>378.12</v>
+      </c>
+      <c r="F311" t="n">
+        <v>382.12</v>
+      </c>
+      <c r="G311" t="n">
+        <v>382.81</v>
+      </c>
+      <c r="H311" t="n">
+        <v>371.63</v>
+      </c>
+      <c r="I311" t="n">
+        <v>361.4</v>
+      </c>
+      <c r="J311" t="n">
+        <v>350.8</v>
+      </c>
+      <c r="K311" t="n">
+        <v>349.66</v>
+      </c>
+      <c r="L311" t="n">
+        <v>351.17</v>
+      </c>
+      <c r="M311" t="n">
+        <v>350.04</v>
+      </c>
+      <c r="N311" t="n">
+        <v>350.89</v>
+      </c>
+      <c r="O311" t="n">
+        <v>353.81</v>
+      </c>
+      <c r="P311" t="n">
+        <v>359.18</v>
+      </c>
+      <c r="Q311" t="n">
+        <v>360.18</v>
+      </c>
+      <c r="R311" t="n">
+        <v>358.02</v>
+      </c>
+      <c r="S311" t="n">
+        <v>358.3</v>
+      </c>
+      <c r="T311" t="n">
+        <v>363.66</v>
+      </c>
+      <c r="U311" t="n">
+        <v>366.92</v>
+      </c>
+      <c r="V311" t="n">
+        <v>355.58</v>
+      </c>
+      <c r="W311" t="n">
+        <v>358.14</v>
+      </c>
+      <c r="X311" t="n">
+        <v>360.13</v>
+      </c>
+      <c r="Y311" t="n">
+        <v>370.82</v>
+      </c>
+      <c r="Z311" t="n">
+        <v>355.36</v>
+      </c>
+      <c r="AA311" t="n">
+        <v>349.31</v>
+      </c>
+      <c r="AB311" t="n">
+        <v>361.13</v>
+      </c>
+      <c r="AC311" t="n">
+        <v>368.93</v>
+      </c>
+      <c r="AD311" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29774,7 +30158,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B324"/>
+  <dimension ref="A1:B328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33017,6 +33401,46 @@
       </c>
       <c r="B324" t="n">
         <v>-0.6</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B325" t="n">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B326" t="n">
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B327" t="n">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B328" t="n">
+        <v>-0.34</v>
       </c>
     </row>
   </sheetData>
@@ -33185,28 +33609,28 @@
         <v>0.0104</v>
       </c>
       <c r="I2" t="n">
-        <v>-6.867543698372222</v>
+        <v>-6.768308390304493</v>
       </c>
       <c r="J2" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="K2" t="n">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="L2" t="n">
-        <v>0.770870355299889</v>
+        <v>0.7673936377067549</v>
       </c>
       <c r="M2" t="n">
-        <v>19.67945860965538</v>
+        <v>19.84119606947541</v>
       </c>
       <c r="N2" t="n">
-        <v>699.7587500518913</v>
+        <v>705.4289642823622</v>
       </c>
       <c r="O2" t="n">
-        <v>26.45295352227972</v>
+        <v>26.5599127310758</v>
       </c>
       <c r="P2" t="n">
-        <v>559.8834283505437</v>
+        <v>558.7553481906954</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -33267,28 +33691,28 @@
         <v>0.0103</v>
       </c>
       <c r="I3" t="n">
-        <v>-3.68333812404501</v>
+        <v>-3.667448771825152</v>
       </c>
       <c r="J3" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="K3" t="n">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4879184084332906</v>
+        <v>0.4939562611818</v>
       </c>
       <c r="M3" t="n">
-        <v>22.2074213911498</v>
+        <v>21.96874743500305</v>
       </c>
       <c r="N3" t="n">
-        <v>776.6896785077483</v>
+        <v>765.0528492558789</v>
       </c>
       <c r="O3" t="n">
-        <v>27.86915281288163</v>
+        <v>27.65958873981822</v>
       </c>
       <c r="P3" t="n">
-        <v>486.6566289583723</v>
+        <v>486.4869305717033</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33345,28 +33769,28 @@
         <v>0.0125</v>
       </c>
       <c r="I4" t="n">
-        <v>2.120542725741029</v>
+        <v>2.050901328270098</v>
       </c>
       <c r="J4" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="K4" t="n">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1656746750892782</v>
+        <v>0.1598880861950959</v>
       </c>
       <c r="M4" t="n">
-        <v>29.45229130972831</v>
+        <v>29.39837793624178</v>
       </c>
       <c r="N4" t="n">
-        <v>1244.991180404753</v>
+        <v>1235.873557030666</v>
       </c>
       <c r="O4" t="n">
-        <v>35.28443255041454</v>
+        <v>35.15499334419886</v>
       </c>
       <c r="P4" t="n">
-        <v>360.1102537075555</v>
+        <v>360.8546876904975</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33423,28 +33847,28 @@
         <v>0.0224</v>
       </c>
       <c r="I5" t="n">
-        <v>1.706424127404367</v>
+        <v>1.653477368371216</v>
       </c>
       <c r="J5" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="K5" t="n">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5399250255871284</v>
+        <v>0.522831623935214</v>
       </c>
       <c r="M5" t="n">
-        <v>9.126302313235874</v>
+        <v>9.243559670921574</v>
       </c>
       <c r="N5" t="n">
-        <v>132.1226493932971</v>
+        <v>135.2470958213741</v>
       </c>
       <c r="O5" t="n">
-        <v>11.49446168349337</v>
+        <v>11.62957848855125</v>
       </c>
       <c r="P5" t="n">
-        <v>353.3986786907386</v>
+        <v>353.9663089461599</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33501,28 +33925,28 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7017088091652999</v>
+        <v>0.6990061985521134</v>
       </c>
       <c r="J6" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="K6" t="n">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4108302980850603</v>
+        <v>0.4163614412205491</v>
       </c>
       <c r="M6" t="n">
-        <v>3.168411423904888</v>
+        <v>3.13812400941566</v>
       </c>
       <c r="N6" t="n">
-        <v>37.36043322464337</v>
+        <v>36.88802409910269</v>
       </c>
       <c r="O6" t="n">
-        <v>6.112318154730116</v>
+        <v>6.073551193420756</v>
       </c>
       <c r="P6" t="n">
-        <v>363.922122807386</v>
+        <v>363.9511803356749</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33579,28 +34003,28 @@
         <v>0.0726</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2406267128112183</v>
+        <v>0.2400996463154866</v>
       </c>
       <c r="J7" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="K7" t="n">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02940230316869863</v>
+        <v>0.03015878434013741</v>
       </c>
       <c r="M7" t="n">
-        <v>4.199686377440052</v>
+        <v>4.149697864000379</v>
       </c>
       <c r="N7" t="n">
-        <v>102.8385211136634</v>
+        <v>101.5000445332092</v>
       </c>
       <c r="O7" t="n">
-        <v>10.14093295085139</v>
+        <v>10.07472304995076</v>
       </c>
       <c r="P7" t="n">
-        <v>376.8712446519681</v>
+        <v>376.8768616990489</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33657,28 +34081,28 @@
         <v>0.0303</v>
       </c>
       <c r="I8" t="n">
-        <v>0.04424051863680493</v>
+        <v>0.04030331818451841</v>
       </c>
       <c r="J8" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="K8" t="n">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001254823106584091</v>
+        <v>0.001073377820786647</v>
       </c>
       <c r="M8" t="n">
-        <v>5.976133237141195</v>
+        <v>5.922149706824269</v>
       </c>
       <c r="N8" t="n">
-        <v>84.27424941015775</v>
+        <v>83.21979607267549</v>
       </c>
       <c r="O8" t="n">
-        <v>9.180100729848107</v>
+        <v>9.122488480270912</v>
       </c>
       <c r="P8" t="n">
-        <v>372.911685890293</v>
+        <v>372.9534735995512</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33735,28 +34159,28 @@
         <v>0.0271</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.03266960778978389</v>
+        <v>-0.04938766779698942</v>
       </c>
       <c r="J9" t="n">
+        <v>310</v>
+      </c>
+      <c r="K9" t="n">
         <v>306</v>
       </c>
-      <c r="K9" t="n">
-        <v>302</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.000447141567260223</v>
+        <v>0.001048653010431111</v>
       </c>
       <c r="M9" t="n">
-        <v>7.834320505240155</v>
+        <v>7.815412102933981</v>
       </c>
       <c r="N9" t="n">
-        <v>129.8977221694291</v>
+        <v>128.726863841919</v>
       </c>
       <c r="O9" t="n">
-        <v>11.39726818888759</v>
+        <v>11.34578617117029</v>
       </c>
       <c r="P9" t="n">
-        <v>370.4382048810846</v>
+        <v>370.6149871242289</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33813,28 +34237,28 @@
         <v>0.0339</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3642566174466654</v>
+        <v>-0.3757064503623938</v>
       </c>
       <c r="J10" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="K10" t="n">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="L10" t="n">
-        <v>0.05142767463941089</v>
+        <v>0.05603796628654001</v>
       </c>
       <c r="M10" t="n">
-        <v>8.177023671575441</v>
+        <v>8.120901455769754</v>
       </c>
       <c r="N10" t="n">
-        <v>130.873193994286</v>
+        <v>129.4230474915682</v>
       </c>
       <c r="O10" t="n">
-        <v>11.43998225498126</v>
+        <v>11.37642507519687</v>
       </c>
       <c r="P10" t="n">
-        <v>366.0842848475595</v>
+        <v>366.2065535032109</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33891,28 +34315,28 @@
         <v>0.0553</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.02797480236590338</v>
+        <v>-0.03776357830436328</v>
       </c>
       <c r="J11" t="n">
+        <v>310</v>
+      </c>
+      <c r="K11" t="n">
         <v>306</v>
       </c>
-      <c r="K11" t="n">
-        <v>302</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.0004871256720044848</v>
+        <v>0.0009131600272680451</v>
       </c>
       <c r="M11" t="n">
-        <v>6.119996232628281</v>
+        <v>6.074058527244333</v>
       </c>
       <c r="N11" t="n">
-        <v>84.97268393940453</v>
+        <v>84.04012436040884</v>
       </c>
       <c r="O11" t="n">
-        <v>9.218062916871665</v>
+        <v>9.167340091891914</v>
       </c>
       <c r="P11" t="n">
-        <v>355.2100716993363</v>
+        <v>355.3155295111535</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33969,28 +34393,28 @@
         <v>0.0609</v>
       </c>
       <c r="I12" t="n">
-        <v>0.113250890369675</v>
+        <v>0.1030552882453737</v>
       </c>
       <c r="J12" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="K12" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="L12" t="n">
-        <v>0.02142952761180927</v>
+        <v>0.01823925380674596</v>
       </c>
       <c r="M12" t="n">
-        <v>4.321282715905624</v>
+        <v>4.312063721638626</v>
       </c>
       <c r="N12" t="n">
-        <v>31.99619702060392</v>
+        <v>31.7801490090141</v>
       </c>
       <c r="O12" t="n">
-        <v>5.656518100439873</v>
+        <v>5.637388491936147</v>
       </c>
       <c r="P12" t="n">
-        <v>351.4595051649501</v>
+        <v>351.5667283877752</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -34047,28 +34471,28 @@
         <v>0.061</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1942683962419198</v>
+        <v>0.1832373718851492</v>
       </c>
       <c r="J13" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="K13" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="L13" t="n">
-        <v>0.09158913815343905</v>
+        <v>0.08380493116533294</v>
       </c>
       <c r="M13" t="n">
-        <v>3.45866529929401</v>
+        <v>3.462445238049775</v>
       </c>
       <c r="N13" t="n">
-        <v>20.44929116467015</v>
+        <v>20.40625231505949</v>
       </c>
       <c r="O13" t="n">
-        <v>4.52208924775597</v>
+        <v>4.517328006140299</v>
       </c>
       <c r="P13" t="n">
-        <v>348.5749354199299</v>
+        <v>348.6909429217795</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -34125,28 +34549,28 @@
         <v>0.0796</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1396146272554357</v>
+        <v>0.1349189335648096</v>
       </c>
       <c r="J14" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="K14" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="L14" t="n">
-        <v>0.04871445405037489</v>
+        <v>0.0468967791184064</v>
       </c>
       <c r="M14" t="n">
-        <v>3.628771756421715</v>
+        <v>3.605896484411087</v>
       </c>
       <c r="N14" t="n">
-        <v>20.79459677147642</v>
+        <v>20.56645728699294</v>
       </c>
       <c r="O14" t="n">
-        <v>4.560109293808255</v>
+        <v>4.535025610400997</v>
       </c>
       <c r="P14" t="n">
-        <v>349.2017970389065</v>
+        <v>349.2511837601756</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -34203,28 +34627,28 @@
         <v>0.108</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2657062446538141</v>
+        <v>0.2579158711552284</v>
       </c>
       <c r="J15" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="K15" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1690875115383901</v>
+        <v>0.1642325446469481</v>
       </c>
       <c r="M15" t="n">
-        <v>3.441332327155652</v>
+        <v>3.434442599865401</v>
       </c>
       <c r="N15" t="n">
-        <v>18.95321456296898</v>
+        <v>18.81911243306731</v>
       </c>
       <c r="O15" t="n">
-        <v>4.353528978078472</v>
+        <v>4.338100094864952</v>
       </c>
       <c r="P15" t="n">
-        <v>349.5484845034526</v>
+        <v>349.6304086397507</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -34281,28 +34705,28 @@
         <v>0.2</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3323315350087228</v>
+        <v>0.3277385326410521</v>
       </c>
       <c r="J16" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="K16" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2320104047076131</v>
+        <v>0.232068123331348</v>
       </c>
       <c r="M16" t="n">
-        <v>3.291113692157971</v>
+        <v>3.27349393909471</v>
       </c>
       <c r="N16" t="n">
-        <v>19.97223117875517</v>
+        <v>19.75963793770703</v>
       </c>
       <c r="O16" t="n">
-        <v>4.469030227997475</v>
+        <v>4.445181429110293</v>
       </c>
       <c r="P16" t="n">
-        <v>351.6610045543754</v>
+        <v>351.7092934674813</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -34359,28 +34783,28 @@
         <v>0.057</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4444997113916731</v>
+        <v>0.4374742748802827</v>
       </c>
       <c r="J17" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="K17" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3538108218749234</v>
+        <v>0.3524427673564691</v>
       </c>
       <c r="M17" t="n">
-        <v>3.364862057955609</v>
+        <v>3.353873050567543</v>
       </c>
       <c r="N17" t="n">
-        <v>19.71365434639733</v>
+        <v>19.54840658464375</v>
       </c>
       <c r="O17" t="n">
-        <v>4.440006120085571</v>
+        <v>4.421358002316002</v>
       </c>
       <c r="P17" t="n">
-        <v>351.0949777270006</v>
+        <v>351.1688629910661</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -34437,28 +34861,28 @@
         <v>0.0491</v>
       </c>
       <c r="I18" t="n">
-        <v>0.542414274304221</v>
+        <v>0.5343917489510003</v>
       </c>
       <c r="J18" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="K18" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="L18" t="n">
-        <v>0.4369481495259527</v>
+        <v>0.4357169479554012</v>
       </c>
       <c r="M18" t="n">
-        <v>3.612650910880788</v>
+        <v>3.606550878021879</v>
       </c>
       <c r="N18" t="n">
-        <v>20.71172677729347</v>
+        <v>20.56026979619381</v>
       </c>
       <c r="O18" t="n">
-        <v>4.551013818622557</v>
+        <v>4.53434336990416</v>
       </c>
       <c r="P18" t="n">
-        <v>346.5161145246752</v>
+        <v>346.6004856169442</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -34515,28 +34939,28 @@
         <v>0.0369</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5677820850137664</v>
+        <v>0.5568107616342175</v>
       </c>
       <c r="J19" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="K19" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4085890594354773</v>
+        <v>0.4044369150390598</v>
       </c>
       <c r="M19" t="n">
-        <v>4.062055734933981</v>
+        <v>4.068393385470623</v>
       </c>
       <c r="N19" t="n">
-        <v>25.4918640696554</v>
+        <v>25.38101525916445</v>
       </c>
       <c r="O19" t="n">
-        <v>5.048946827770659</v>
+        <v>5.03795744912206</v>
       </c>
       <c r="P19" t="n">
-        <v>347.3811219275146</v>
+        <v>347.4965073107638</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -34593,28 +35017,28 @@
         <v>0.0413</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5841995749841096</v>
+        <v>0.5731710011417328</v>
       </c>
       <c r="J20" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="K20" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3807365372236809</v>
+        <v>0.3772165082985414</v>
       </c>
       <c r="M20" t="n">
-        <v>4.465406097377816</v>
+        <v>4.468472839879091</v>
       </c>
       <c r="N20" t="n">
-        <v>30.32557032461435</v>
+        <v>30.15307363854953</v>
       </c>
       <c r="O20" t="n">
-        <v>5.506865744197361</v>
+        <v>5.491181442872702</v>
       </c>
       <c r="P20" t="n">
-        <v>352.3375203730639</v>
+        <v>352.4535087062669</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -34671,28 +35095,28 @@
         <v>0.0369</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6256184020046525</v>
+        <v>0.6122022714558635</v>
       </c>
       <c r="J21" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="K21" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="L21" t="n">
-        <v>0.3702147453175354</v>
+        <v>0.365121400868206</v>
       </c>
       <c r="M21" t="n">
-        <v>5.094347382549163</v>
+        <v>5.099383524114809</v>
       </c>
       <c r="N21" t="n">
-        <v>36.37419643281859</v>
+        <v>36.2293080675275</v>
       </c>
       <c r="O21" t="n">
-        <v>6.031102422676852</v>
+        <v>6.019078672648123</v>
       </c>
       <c r="P21" t="n">
-        <v>355.3672472735802</v>
+        <v>355.5083491411332</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -34749,28 +35173,28 @@
         <v>0.0313</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5314952493520563</v>
+        <v>0.4999881360865202</v>
       </c>
       <c r="J22" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="K22" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2092906879547326</v>
+        <v>0.1897562222562504</v>
       </c>
       <c r="M22" t="n">
-        <v>6.517800003212376</v>
+        <v>6.611206651747881</v>
       </c>
       <c r="N22" t="n">
-        <v>58.30439922069374</v>
+        <v>59.34113451655787</v>
       </c>
       <c r="O22" t="n">
-        <v>7.635731741011711</v>
+        <v>7.703319707538943</v>
       </c>
       <c r="P22" t="n">
-        <v>352.7087885544305</v>
+        <v>353.0401333805091</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -34827,28 +35251,28 @@
         <v>0.0262</v>
       </c>
       <c r="I23" t="n">
-        <v>0.955771955262767</v>
+        <v>0.9293971374875176</v>
       </c>
       <c r="J23" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="K23" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="L23" t="n">
-        <v>0.5303795308781518</v>
+        <v>0.5169505287532343</v>
       </c>
       <c r="M23" t="n">
-        <v>5.410586966989724</v>
+        <v>5.475429787846841</v>
       </c>
       <c r="N23" t="n">
-        <v>44.18800882465493</v>
+        <v>44.8706184870281</v>
       </c>
       <c r="O23" t="n">
-        <v>6.647406172685322</v>
+        <v>6.698553462280352</v>
       </c>
       <c r="P23" t="n">
-        <v>343.190877951876</v>
+        <v>343.4682654448451</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -34905,28 +35329,28 @@
         <v>0.0362</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6622059938344227</v>
+        <v>0.6349617273365084</v>
       </c>
       <c r="J24" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="K24" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="L24" t="n">
-        <v>0.4114960646514764</v>
+        <v>0.3890503373069419</v>
       </c>
       <c r="M24" t="n">
-        <v>4.867112794027684</v>
+        <v>4.937361111730457</v>
       </c>
       <c r="N24" t="n">
-        <v>34.26143134428185</v>
+        <v>35.1974741150508</v>
       </c>
       <c r="O24" t="n">
-        <v>5.853326519534157</v>
+        <v>5.932745916946957</v>
       </c>
       <c r="P24" t="n">
-        <v>354.4167602876792</v>
+        <v>354.7033283531902</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -34983,28 +35407,28 @@
         <v>0.0481</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6833142470050934</v>
+        <v>0.6598000829870979</v>
       </c>
       <c r="J25" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="K25" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="L25" t="n">
-        <v>0.4349328649872772</v>
+        <v>0.4179138080572175</v>
       </c>
       <c r="M25" t="n">
-        <v>4.795422291331686</v>
+        <v>4.829172618821649</v>
       </c>
       <c r="N25" t="n">
-        <v>33.14014296226723</v>
+        <v>33.70870557260113</v>
       </c>
       <c r="O25" t="n">
-        <v>5.756747602793371</v>
+        <v>5.80591987307792</v>
       </c>
       <c r="P25" t="n">
-        <v>361.8780016910218</v>
+        <v>362.1253055078912</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -35061,28 +35485,28 @@
         <v>0.0572</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5733249821487754</v>
+        <v>0.5541193018905179</v>
       </c>
       <c r="J26" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="K26" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="L26" t="n">
-        <v>0.3763731461661275</v>
+        <v>0.3623284018372673</v>
       </c>
       <c r="M26" t="n">
-        <v>4.383712532151592</v>
+        <v>4.422020639389352</v>
       </c>
       <c r="N26" t="n">
-        <v>29.75387359635577</v>
+        <v>30.0412514146385</v>
       </c>
       <c r="O26" t="n">
-        <v>5.454711137755671</v>
+        <v>5.480990003150754</v>
       </c>
       <c r="P26" t="n">
-        <v>347.4595969185627</v>
+        <v>347.6615699895598</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -35139,28 +35563,28 @@
         <v>0.0602</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3874157072157938</v>
+        <v>0.3696788152748224</v>
       </c>
       <c r="J27" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="K27" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="L27" t="n">
-        <v>0.2422593689205697</v>
+        <v>0.2269136434271091</v>
       </c>
       <c r="M27" t="n">
-        <v>3.961480931962844</v>
+        <v>4.005592308974248</v>
       </c>
       <c r="N27" t="n">
-        <v>25.64661460489644</v>
+        <v>25.88411345697865</v>
       </c>
       <c r="O27" t="n">
-        <v>5.064248671313094</v>
+        <v>5.087643212429371</v>
       </c>
       <c r="P27" t="n">
-        <v>345.2980112102618</v>
+        <v>345.4845373973989</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -35217,28 +35641,28 @@
         <v>0.0598</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2228791079763912</v>
+        <v>0.2065552974570778</v>
       </c>
       <c r="J28" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="K28" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="L28" t="n">
-        <v>0.09019421174080711</v>
+        <v>0.07939317310254168</v>
       </c>
       <c r="M28" t="n">
-        <v>4.083533087985179</v>
+        <v>4.111489135604843</v>
       </c>
       <c r="N28" t="n">
-        <v>27.37438384654207</v>
+        <v>27.50302567829849</v>
       </c>
       <c r="O28" t="n">
-        <v>5.232053501880698</v>
+        <v>5.24433272002249</v>
       </c>
       <c r="P28" t="n">
-        <v>360.9647871451089</v>
+        <v>361.1364522414372</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -35295,28 +35719,28 @@
         <v>0.0559</v>
       </c>
       <c r="I29" t="n">
-        <v>0.09589161918895178</v>
+        <v>0.07880128030286083</v>
       </c>
       <c r="J29" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="K29" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="L29" t="n">
-        <v>0.02514206810169495</v>
+        <v>0.01716956820876703</v>
       </c>
       <c r="M29" t="n">
-        <v>3.353147116922431</v>
+        <v>3.40260448706091</v>
       </c>
       <c r="N29" t="n">
-        <v>19.4776805145872</v>
+        <v>19.76070963594502</v>
       </c>
       <c r="O29" t="n">
-        <v>4.41335252552832</v>
+        <v>4.44530197353847</v>
       </c>
       <c r="P29" t="n">
-        <v>372.412552179019</v>
+        <v>372.5922706363685</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -35354,7 +35778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD307"/>
+  <dimension ref="A1:AD311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81490,7 +81914,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>-36.66891732473826,175.5576633281517</t>
+          <t>-36.66883521950195,175.5573771962967</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -81624,6 +82048,614 @@
         </is>
       </c>
       <c r="AD307" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>-36.6682247509552,175.55791628582585</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>-36.6688510299545,175.55743229454384</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>-36.669518778587644,175.55709284253734</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>-36.670151635012694,175.55663181388442</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>-36.67082599204737,175.55631543242487</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>-36.67148445712025,175.5560247086202</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>-36.672162072294874,175.55580448083077</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>-36.67286845514315,175.555603366115</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>-36.67357459662697,175.55537670029176</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>-36.67428895775063,175.5552557904518</t>
+        </is>
+      </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>-36.67500390970432,175.55514256172356</t>
+        </is>
+      </c>
+      <c r="M308" t="inlineStr">
+        <is>
+          <t>-36.67571976813536,175.55502163965454</t>
+        </is>
+      </c>
+      <c r="N308" t="inlineStr">
+        <is>
+          <t>-36.676440266358206,175.55496481559754</t>
+        </is>
+      </c>
+      <c r="O308" t="inlineStr">
+        <is>
+          <t>-36.6771595543761,175.5549134744839</t>
+        </is>
+      </c>
+      <c r="P308" t="inlineStr">
+        <is>
+          <t>-36.67788121091193,175.55488944502065</t>
+        </is>
+      </c>
+      <c r="Q308" t="inlineStr">
+        <is>
+          <t>-36.67859929816149,175.55491882210035</t>
+        </is>
+      </c>
+      <c r="R308" t="inlineStr">
+        <is>
+          <t>-36.6793182291149,175.55499081555453</t>
+        </is>
+      </c>
+      <c r="S308" t="inlineStr">
+        <is>
+          <t>-36.680033514346796,175.55509712420502</t>
+        </is>
+      </c>
+      <c r="T308" t="inlineStr">
+        <is>
+          <t>-36.68074313363615,175.55525217639357</t>
+        </is>
+      </c>
+      <c r="U308" t="inlineStr">
+        <is>
+          <t>-36.681444264059564,175.555425939533</t>
+        </is>
+      </c>
+      <c r="V308" t="inlineStr">
+        <is>
+          <t>-36.682169111022624,175.55551704170824</t>
+        </is>
+      </c>
+      <c r="W308" t="inlineStr">
+        <is>
+          <t>-36.68285428081452,175.555796065716</t>
+        </is>
+      </c>
+      <c r="X308" t="inlineStr">
+        <is>
+          <t>-36.6835355186104,175.55609219470222</t>
+        </is>
+      </c>
+      <c r="Y308" t="inlineStr">
+        <is>
+          <t>-36.68419761865407,175.55638839819068</t>
+        </is>
+      </c>
+      <c r="Z308" t="inlineStr">
+        <is>
+          <t>-36.6848569418306,175.55674397762232</t>
+        </is>
+      </c>
+      <c r="AA308" t="inlineStr">
+        <is>
+          <t>-36.68546147402868,175.5572413590627</t>
+        </is>
+      </c>
+      <c r="AB308" t="inlineStr">
+        <is>
+          <t>-36.68596629459889,175.5578927116583</t>
+        </is>
+      </c>
+      <c r="AC308" t="inlineStr">
+        <is>
+          <t>-36.68632227907664,175.55866396897667</t>
+        </is>
+      </c>
+      <c r="AD308" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>-36.66821238688756,175.5578731978245</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>-36.66886145939726,175.5574686404355</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>-36.66950502371649,175.5570449077272</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>-36.670142172781915,175.55659883870896</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>-36.6708278059019,175.55632175359773</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>-36.67148506171418,175.55602786389366</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>-36.67215984935748,175.55577958129217</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>-36.672865935303626,175.55557097127826</t>
+        </is>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>-36.67357201612834,175.55534352589578</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>-36.6742870873125,175.55523174435797</t>
+        </is>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>-36.67500198730029,175.5551178474534</t>
+        </is>
+      </c>
+      <c r="M309" t="inlineStr">
+        <is>
+          <t>-36.67571924477295,175.55501361310937</t>
+        </is>
+      </c>
+      <c r="N309" t="inlineStr">
+        <is>
+          <t>-36.676440116231525,175.55496191359373</t>
+        </is>
+      </c>
+      <c r="O309" t="inlineStr">
+        <is>
+          <t>-36.677159911690254,175.55492050683813</t>
+        </is>
+      </c>
+      <c r="P309" t="inlineStr">
+        <is>
+          <t>-36.677881571128374,175.55490923698994</t>
+        </is>
+      </c>
+      <c r="Q309" t="inlineStr">
+        <is>
+          <t>-36.67859922658644,175.55492004922198</t>
+        </is>
+      </c>
+      <c r="R309" t="inlineStr">
+        <is>
+          <t>-36.679318183705014,175.5549912593869</t>
+        </is>
+      </c>
+      <c r="S309" t="inlineStr">
+        <is>
+          <t>-36.68003442255181,175.55508824747736</t>
+        </is>
+      </c>
+      <c r="T309" t="inlineStr">
+        <is>
+          <t>-36.680743266789314,175.55525107016055</t>
+        </is>
+      </c>
+      <c r="U309" t="inlineStr">
+        <is>
+          <t>-36.6814447844896,175.55542310405076</t>
+        </is>
+      </c>
+      <c r="V309" t="inlineStr">
+        <is>
+          <t>-36.682169111022624,175.55551704170824</t>
+        </is>
+      </c>
+      <c r="W309" t="inlineStr">
+        <is>
+          <t>-36.68285474989969,175.55579402183452</t>
+        </is>
+      </c>
+      <c r="X309" t="inlineStr">
+        <is>
+          <t>-36.68354596201151,175.55604669107788</t>
+        </is>
+      </c>
+      <c r="Y309" t="inlineStr">
+        <is>
+          <t>-36.68420113701063,175.55637957721717</t>
+        </is>
+      </c>
+      <c r="Z309" t="inlineStr">
+        <is>
+          <t>-36.68484883345015,175.55675697845868</t>
+        </is>
+      </c>
+      <c r="AA309" t="inlineStr">
+        <is>
+          <t>-36.68545933593598,175.55724467876303</t>
+        </is>
+      </c>
+      <c r="AB309" t="inlineStr">
+        <is>
+          <t>-36.68596107091466,175.55789871366594</t>
+        </is>
+      </c>
+      <c r="AC309" t="inlineStr">
+        <is>
+          <t>-36.68631205892524,175.5586725609292</t>
+        </is>
+      </c>
+      <c r="AD309" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>-36.66821740506855,175.55789068586262</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>-36.6688705586988,175.55750035091665</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>-36.66951394171216,175.55707598633853</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>-36.670149911859546,175.55662580881997</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>-36.67082841051998,175.5563238606554</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>-36.67148568715608,175.5560311279697</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>-36.67216062341663,175.5557882516671</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>-36.672867372738956,175.5555894508069</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>-36.67357307257522,175.5553571073597</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>-36.67428788398119,175.55524198621265</t>
+        </is>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>-36.67500338147671,175.55513577086543</t>
+        </is>
+      </c>
+      <c r="M310" t="inlineStr">
+        <is>
+          <t>-36.67571967363943,175.55502019041722</t>
+        </is>
+      </c>
+      <c r="N310" t="inlineStr">
+        <is>
+          <t>-36.67644034142154,175.55496626659948</t>
+        </is>
+      </c>
+      <c r="O310" t="inlineStr">
+        <is>
+          <t>-36.677160036466525,175.5549229625809</t>
+        </is>
+      </c>
+      <c r="P310" t="inlineStr">
+        <is>
+          <t>-36.67788156298793,175.5549087897138</t>
+        </is>
+      </c>
+      <c r="Q310" t="inlineStr">
+        <is>
+          <t>-36.67859902487486,175.55492350747375</t>
+        </is>
+      </c>
+      <c r="R310" t="inlineStr">
+        <is>
+          <t>-36.67931807018031,175.55499236896773</t>
+        </is>
+      </c>
+      <c r="S310" t="inlineStr">
+        <is>
+          <t>-36.680033400821145,175.55509823379595</t>
+        </is>
+      </c>
+      <c r="T310" t="inlineStr">
+        <is>
+          <t>-36.68074313363615,175.55525217639357</t>
+        </is>
+      </c>
+      <c r="U310" t="inlineStr">
+        <is>
+          <t>-36.68144558515106,175.55541874177035</t>
+        </is>
+      </c>
+      <c r="V310" t="inlineStr">
+        <is>
+          <t>-36.68216701250054,175.55552618531468</t>
+        </is>
+      </c>
+      <c r="W310" t="inlineStr">
+        <is>
+          <t>-36.682853416710174,175.5557998307608</t>
+        </is>
+      </c>
+      <c r="X310" t="inlineStr">
+        <is>
+          <t>-36.68354393752372,175.55605551211247</t>
+        </is>
+      </c>
+      <c r="Y310" t="inlineStr">
+        <is>
+          <t>-36.68419885807522,175.55638529080235</t>
+        </is>
+      </c>
+      <c r="Z310" t="inlineStr">
+        <is>
+          <t>-36.684844972316135,175.55676316933216</t>
+        </is>
+      </c>
+      <c r="AA310" t="inlineStr">
+        <is>
+          <t>-36.68545562240637,175.5572504445579</t>
+        </is>
+      </c>
+      <c r="AB310" t="inlineStr">
+        <is>
+          <t>-36.68595981458549,175.55790015718665</t>
+        </is>
+      </c>
+      <c r="AC310" t="inlineStr">
+        <is>
+          <t>-36.686305941754064,175.55867770355664</t>
+        </is>
+      </c>
+      <c r="AD310" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:48+00:00</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>-36.66821284033776,175.55787477806882</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>-36.66886611485496,175.55748486440174</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>-36.66950097282755,175.55703079066535</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>-36.67014277739758,175.5566009457487</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>-36.67082919652346,175.55632659983044</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>-36.671484248639565,175.55602362059489</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>-36.672159551642245,175.55577624653262</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>-36.672865112673676,175.55556039564462</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>-36.673571773664904,175.5553404088385</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>-36.674286619702194,175.55522573283466</t>
+        </is>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>-36.67500375383391,175.55514055786378</t>
+        </is>
+      </c>
+      <c r="M311" t="inlineStr">
+        <is>
+          <t>-36.675720029816375,175.55502565292716</t>
+        </is>
+      </c>
+      <c r="N311" t="inlineStr">
+        <is>
+          <t>-36.676440046942254,175.55496057420737</t>
+        </is>
+      </c>
+      <c r="O311" t="inlineStr">
+        <is>
+          <t>-36.67715993437686,175.55492095333682</t>
+        </is>
+      </c>
+      <c r="P311" t="inlineStr">
+        <is>
+          <t>-36.67788155281237,175.55490823061862</t>
+        </is>
+      </c>
+      <c r="Q311" t="inlineStr">
+        <is>
+          <t>-36.67859928514784,175.55491904521338</t>
+        </is>
+      </c>
+      <c r="R311" t="inlineStr">
+        <is>
+          <t>-36.67931805882784,175.55499247992586</t>
+        </is>
+      </c>
+      <c r="S311" t="inlineStr">
+        <is>
+          <t>-36.68003388898144,175.5550934625549</t>
+        </is>
+      </c>
+      <c r="T311" t="inlineStr">
+        <is>
+          <t>-36.68074333336589,175.55525051704407</t>
+        </is>
+      </c>
+      <c r="U311" t="inlineStr">
+        <is>
+          <t>-36.68144502468806,175.55542179536667</t>
+        </is>
+      </c>
+      <c r="V311" t="inlineStr">
+        <is>
+          <t>-36.682166148403006,175.55552995032892</t>
+        </is>
+      </c>
+      <c r="W311" t="inlineStr">
+        <is>
+          <t>-36.68285591026811,175.555788965917</t>
+        </is>
+      </c>
+      <c r="X311" t="inlineStr">
+        <is>
+          <t>-36.68354707301063,175.55604185026598</t>
+        </is>
+      </c>
+      <c r="Y311" t="inlineStr">
+        <is>
+          <t>-36.684201097029316,175.5563796774555</t>
+        </is>
+      </c>
+      <c r="Z311" t="inlineStr">
+        <is>
+          <t>-36.68485098465325,175.5567535292575</t>
+        </is>
+      </c>
+      <c r="AA311" t="inlineStr">
+        <is>
+          <t>-36.68545562240637,175.5572504445579</t>
+        </is>
+      </c>
+      <c r="AB311" t="inlineStr">
+        <is>
+          <t>-36.685958558256324,175.5579016007073</t>
+        </is>
+      </c>
+      <c r="AC311" t="inlineStr">
+        <is>
+          <t>-36.68630870194109,175.5586753831029</t>
+        </is>
+      </c>
+      <c r="AD311" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0150/nzd0150.xlsx
+++ b/data/nzd0150/nzd0150.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD311"/>
+  <dimension ref="A1:AD312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30144,6 +30144,102 @@
       <c r="AD311" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B312" t="n">
+        <v>410.96</v>
+      </c>
+      <c r="C312" t="n">
+        <v>405.11</v>
+      </c>
+      <c r="D312" t="n">
+        <v>392.44</v>
+      </c>
+      <c r="E312" t="n">
+        <v>380.6</v>
+      </c>
+      <c r="F312" t="n">
+        <v>382.62</v>
+      </c>
+      <c r="G312" t="n">
+        <v>383.42</v>
+      </c>
+      <c r="H312" t="n">
+        <v>373.55</v>
+      </c>
+      <c r="I312" t="n">
+        <v>363.09</v>
+      </c>
+      <c r="J312" t="n">
+        <v>352.82</v>
+      </c>
+      <c r="K312" t="n">
+        <v>350.84</v>
+      </c>
+      <c r="L312" t="n">
+        <v>352.58</v>
+      </c>
+      <c r="M312" t="n">
+        <v>351.19</v>
+      </c>
+      <c r="N312" t="n">
+        <v>351.61</v>
+      </c>
+      <c r="O312" t="n">
+        <v>354.2</v>
+      </c>
+      <c r="P312" t="n">
+        <v>359.35</v>
+      </c>
+      <c r="Q312" t="n">
+        <v>360.95</v>
+      </c>
+      <c r="R312" t="n">
+        <v>359.01</v>
+      </c>
+      <c r="S312" t="n">
+        <v>359.58</v>
+      </c>
+      <c r="T312" t="n">
+        <v>364.38</v>
+      </c>
+      <c r="U312" t="n">
+        <v>367.86</v>
+      </c>
+      <c r="V312" t="n">
+        <v>357</v>
+      </c>
+      <c r="W312" t="n">
+        <v>359.23</v>
+      </c>
+      <c r="X312" t="n">
+        <v>361.51</v>
+      </c>
+      <c r="Y312" t="n">
+        <v>372.08</v>
+      </c>
+      <c r="Z312" t="n">
+        <v>356.18</v>
+      </c>
+      <c r="AA312" t="n">
+        <v>350.41</v>
+      </c>
+      <c r="AB312" t="n">
+        <v>362.04</v>
+      </c>
+      <c r="AC312" t="n">
+        <v>369.86</v>
+      </c>
+      <c r="AD312" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -30158,7 +30254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B328"/>
+  <dimension ref="A1:B330"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33441,6 +33537,26 @@
       </c>
       <c r="B328" t="n">
         <v>-0.34</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B329" t="n">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>2026-08-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B330" t="n">
+        <v>0.12</v>
       </c>
     </row>
   </sheetData>
@@ -33609,28 +33725,28 @@
         <v>0.0104</v>
       </c>
       <c r="I2" t="n">
-        <v>-6.768308390304493</v>
+        <v>-6.743962223297467</v>
       </c>
       <c r="J2" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K2" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7673936377067549</v>
+        <v>0.7665002540512934</v>
       </c>
       <c r="M2" t="n">
-        <v>19.84119606947541</v>
+        <v>19.88720238449401</v>
       </c>
       <c r="N2" t="n">
-        <v>705.4289642823622</v>
+        <v>706.8485830688849</v>
       </c>
       <c r="O2" t="n">
-        <v>26.5599127310758</v>
+        <v>26.58662413825578</v>
       </c>
       <c r="P2" t="n">
-        <v>558.7553481906954</v>
+        <v>558.4779741907277</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -33691,28 +33807,28 @@
         <v>0.0103</v>
       </c>
       <c r="I3" t="n">
-        <v>-3.667448771825152</v>
+        <v>-3.6558835416393</v>
       </c>
       <c r="J3" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K3" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4939562611818</v>
+        <v>0.4939825053221673</v>
       </c>
       <c r="M3" t="n">
-        <v>21.96874743500305</v>
+        <v>21.94303140834575</v>
       </c>
       <c r="N3" t="n">
-        <v>765.0528492558789</v>
+        <v>763.3900843741026</v>
       </c>
       <c r="O3" t="n">
-        <v>27.65958873981822</v>
+        <v>27.62951473287402</v>
       </c>
       <c r="P3" t="n">
-        <v>486.4869305717033</v>
+        <v>486.3637816235265</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33769,28 +33885,28 @@
         <v>0.0125</v>
       </c>
       <c r="I4" t="n">
-        <v>2.050901328270098</v>
+        <v>2.034766937053583</v>
       </c>
       <c r="J4" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K4" t="n">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1598880861950959</v>
+        <v>0.1585852747948256</v>
       </c>
       <c r="M4" t="n">
-        <v>29.39837793624178</v>
+        <v>29.3780778932007</v>
       </c>
       <c r="N4" t="n">
-        <v>1235.873557030666</v>
+        <v>1233.402822215884</v>
       </c>
       <c r="O4" t="n">
-        <v>35.15499334419886</v>
+        <v>35.11983516783476</v>
       </c>
       <c r="P4" t="n">
-        <v>360.8546876904975</v>
+        <v>361.0275560673739</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33847,28 +33963,28 @@
         <v>0.0224</v>
       </c>
       <c r="I5" t="n">
-        <v>1.653477368371216</v>
+        <v>1.641634496889772</v>
       </c>
       <c r="J5" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K5" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L5" t="n">
-        <v>0.522831623935214</v>
+        <v>0.5192664560727099</v>
       </c>
       <c r="M5" t="n">
-        <v>9.243559670921574</v>
+        <v>9.268482251354747</v>
       </c>
       <c r="N5" t="n">
-        <v>135.2470958213741</v>
+        <v>135.8134887813925</v>
       </c>
       <c r="O5" t="n">
-        <v>11.62957848855125</v>
+        <v>11.65390444363572</v>
       </c>
       <c r="P5" t="n">
-        <v>353.9663089461599</v>
+        <v>354.0935502299918</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33925,28 +34041,28 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6990061985521134</v>
+        <v>0.6989700936593111</v>
       </c>
       <c r="J6" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K6" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4163614412205491</v>
+        <v>0.4181676637551964</v>
       </c>
       <c r="M6" t="n">
-        <v>3.13812400941566</v>
+        <v>3.128081115541741</v>
       </c>
       <c r="N6" t="n">
-        <v>36.88802409910269</v>
+        <v>36.76826711324419</v>
       </c>
       <c r="O6" t="n">
-        <v>6.073551193420756</v>
+        <v>6.063684285419566</v>
       </c>
       <c r="P6" t="n">
-        <v>363.9511803356749</v>
+        <v>363.9515695139794</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34003,28 +34119,28 @@
         <v>0.0726</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2400996463154866</v>
+        <v>0.2401739453947424</v>
       </c>
       <c r="J7" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K7" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03015878434013741</v>
+        <v>0.03039575205754375</v>
       </c>
       <c r="M7" t="n">
-        <v>4.149697864000379</v>
+        <v>4.136464163675124</v>
       </c>
       <c r="N7" t="n">
-        <v>101.5000445332092</v>
+        <v>101.1705395093069</v>
       </c>
       <c r="O7" t="n">
-        <v>10.07472304995076</v>
+        <v>10.05835670024219</v>
       </c>
       <c r="P7" t="n">
-        <v>376.8768616990489</v>
+        <v>376.8760681235476</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34081,28 +34197,28 @@
         <v>0.0303</v>
       </c>
       <c r="I8" t="n">
-        <v>0.04030331818451841</v>
+        <v>0.0399861588748625</v>
       </c>
       <c r="J8" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K8" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001073377820786647</v>
+        <v>0.001064440912879383</v>
       </c>
       <c r="M8" t="n">
-        <v>5.922149706824269</v>
+        <v>5.904895913559741</v>
       </c>
       <c r="N8" t="n">
-        <v>83.21979607267549</v>
+        <v>82.9512209872285</v>
       </c>
       <c r="O8" t="n">
-        <v>9.122488480270912</v>
+        <v>9.107756089577085</v>
       </c>
       <c r="P8" t="n">
-        <v>372.9534735995512</v>
+        <v>372.9568456052849</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34159,28 +34275,28 @@
         <v>0.0271</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.04938766779698942</v>
+        <v>-0.05346991596587025</v>
       </c>
       <c r="J9" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K9" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001048653010431111</v>
+        <v>0.001236940099117123</v>
       </c>
       <c r="M9" t="n">
-        <v>7.815412102933981</v>
+        <v>7.81038580497558</v>
       </c>
       <c r="N9" t="n">
-        <v>128.726863841919</v>
+        <v>128.4315167099088</v>
       </c>
       <c r="O9" t="n">
-        <v>11.34578617117029</v>
+        <v>11.33276297775211</v>
       </c>
       <c r="P9" t="n">
-        <v>370.6149871242289</v>
+        <v>370.6582442630078</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34237,28 +34353,28 @@
         <v>0.0339</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3757064503623938</v>
+        <v>-0.3779145910432393</v>
       </c>
       <c r="J10" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K10" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L10" t="n">
-        <v>0.05603796628654001</v>
+        <v>0.05704830561629215</v>
       </c>
       <c r="M10" t="n">
-        <v>8.120901455769754</v>
+        <v>8.104352050312432</v>
       </c>
       <c r="N10" t="n">
-        <v>129.4230474915682</v>
+        <v>129.0396338822534</v>
       </c>
       <c r="O10" t="n">
-        <v>11.37642507519687</v>
+        <v>11.35956134198207</v>
       </c>
       <c r="P10" t="n">
-        <v>366.2065535032109</v>
+        <v>366.2301805149739</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -34315,28 +34431,28 @@
         <v>0.0553</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.03776357830436328</v>
+        <v>-0.04008778788009808</v>
       </c>
       <c r="J11" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K11" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0009131600272680451</v>
+        <v>0.001036180971406564</v>
       </c>
       <c r="M11" t="n">
-        <v>6.074058527244333</v>
+        <v>6.06241342008477</v>
       </c>
       <c r="N11" t="n">
-        <v>84.04012436040884</v>
+        <v>83.80509932810344</v>
       </c>
       <c r="O11" t="n">
-        <v>9.167340091891914</v>
+        <v>9.154512511767267</v>
       </c>
       <c r="P11" t="n">
-        <v>355.3155295111535</v>
+        <v>355.3406187359233</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -34393,28 +34509,28 @@
         <v>0.0609</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1030552882453737</v>
+        <v>0.1019186266648813</v>
       </c>
       <c r="J12" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K12" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01823925380674596</v>
+        <v>0.01797139120260971</v>
       </c>
       <c r="M12" t="n">
-        <v>4.312063721638626</v>
+        <v>4.303365870966604</v>
       </c>
       <c r="N12" t="n">
-        <v>31.7801490090141</v>
+        <v>31.68764708560627</v>
       </c>
       <c r="O12" t="n">
-        <v>5.637388491936147</v>
+        <v>5.629178189185901</v>
       </c>
       <c r="P12" t="n">
-        <v>351.5667283877752</v>
+        <v>351.5787095907391</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -34471,28 +34587,28 @@
         <v>0.061</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1832373718851492</v>
+        <v>0.1816656010621808</v>
       </c>
       <c r="J13" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K13" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L13" t="n">
-        <v>0.08380493116533294</v>
+        <v>0.08298550605482524</v>
       </c>
       <c r="M13" t="n">
-        <v>3.462445238049775</v>
+        <v>3.458211007307625</v>
       </c>
       <c r="N13" t="n">
-        <v>20.40625231505949</v>
+        <v>20.35915637542257</v>
       </c>
       <c r="O13" t="n">
-        <v>4.517328006140299</v>
+        <v>4.512112185598068</v>
       </c>
       <c r="P13" t="n">
-        <v>348.6909429217795</v>
+        <v>348.7075104785314</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -34549,28 +34665,28 @@
         <v>0.0796</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1349189335648096</v>
+        <v>0.1340995401170645</v>
       </c>
       <c r="J14" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K14" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0468967791184064</v>
+        <v>0.04667338685617028</v>
       </c>
       <c r="M14" t="n">
-        <v>3.605896484411087</v>
+        <v>3.598450327459683</v>
       </c>
       <c r="N14" t="n">
-        <v>20.56645728699294</v>
+        <v>20.50536017130922</v>
       </c>
       <c r="O14" t="n">
-        <v>4.535025610400997</v>
+        <v>4.528284462278095</v>
       </c>
       <c r="P14" t="n">
-        <v>349.2511837601756</v>
+        <v>349.2598207365396</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -34627,28 +34743,28 @@
         <v>0.108</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2579158711552284</v>
+        <v>0.256392489754112</v>
       </c>
       <c r="J15" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K15" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1642325446469481</v>
+        <v>0.1634988040752771</v>
       </c>
       <c r="M15" t="n">
-        <v>3.434442599865401</v>
+        <v>3.430676176336618</v>
       </c>
       <c r="N15" t="n">
-        <v>18.81911243306731</v>
+        <v>18.7759971157253</v>
       </c>
       <c r="O15" t="n">
-        <v>4.338100094864952</v>
+        <v>4.333127867456176</v>
       </c>
       <c r="P15" t="n">
-        <v>349.6304086397507</v>
+        <v>349.6464661383689</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -34705,28 +34821,28 @@
         <v>0.2</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3277385326410521</v>
+        <v>0.3269974056231663</v>
       </c>
       <c r="J16" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K16" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L16" t="n">
-        <v>0.232068123331348</v>
+        <v>0.2325465970861795</v>
       </c>
       <c r="M16" t="n">
-        <v>3.27349393909471</v>
+        <v>3.266995014156294</v>
       </c>
       <c r="N16" t="n">
-        <v>19.75963793770703</v>
+        <v>19.70021954124911</v>
       </c>
       <c r="O16" t="n">
-        <v>4.445181429110293</v>
+        <v>4.438492935811559</v>
       </c>
       <c r="P16" t="n">
-        <v>351.7092934674813</v>
+        <v>351.7171054612846</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -34783,28 +34899,28 @@
         <v>0.057</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4374742748802827</v>
+        <v>0.4362120372486998</v>
       </c>
       <c r="J17" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K17" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3524427673564691</v>
+        <v>0.3526774409605975</v>
       </c>
       <c r="M17" t="n">
-        <v>3.353873050567543</v>
+        <v>3.348890746246294</v>
       </c>
       <c r="N17" t="n">
-        <v>19.54840658464375</v>
+        <v>19.49749320175451</v>
       </c>
       <c r="O17" t="n">
-        <v>4.421358002316002</v>
+        <v>4.415596585032934</v>
       </c>
       <c r="P17" t="n">
-        <v>351.1688629910661</v>
+        <v>351.1821678528755</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -34861,28 +34977,28 @@
         <v>0.0491</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5343917489510003</v>
+        <v>0.5331488833381224</v>
       </c>
       <c r="J18" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K18" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L18" t="n">
-        <v>0.4357169479554012</v>
+        <v>0.4362574302764544</v>
       </c>
       <c r="M18" t="n">
-        <v>3.606550878021879</v>
+        <v>3.601181836361675</v>
       </c>
       <c r="N18" t="n">
-        <v>20.56026979619381</v>
+        <v>20.50573905281087</v>
       </c>
       <c r="O18" t="n">
-        <v>4.53434336990416</v>
+        <v>4.5283262970783</v>
       </c>
       <c r="P18" t="n">
-        <v>346.6004856169442</v>
+        <v>346.6135862842142</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -34939,28 +35055,28 @@
         <v>0.0369</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5568107616342175</v>
+        <v>0.5549669894431261</v>
       </c>
       <c r="J19" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K19" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4044369150390598</v>
+        <v>0.4043837750260082</v>
       </c>
       <c r="M19" t="n">
-        <v>4.068393385470623</v>
+        <v>4.065141623178593</v>
       </c>
       <c r="N19" t="n">
-        <v>25.38101525916445</v>
+        <v>25.32488748370011</v>
       </c>
       <c r="O19" t="n">
-        <v>5.03795744912206</v>
+        <v>5.032383876822207</v>
       </c>
       <c r="P19" t="n">
-        <v>347.4965073107638</v>
+        <v>347.515941950959</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -35017,28 +35133,28 @@
         <v>0.0413</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5731710011417328</v>
+        <v>0.5709410775428457</v>
       </c>
       <c r="J20" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K20" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3772165082985414</v>
+        <v>0.3768369794106136</v>
       </c>
       <c r="M20" t="n">
-        <v>4.468472839879091</v>
+        <v>4.466438765298427</v>
       </c>
       <c r="N20" t="n">
-        <v>30.15307363854953</v>
+        <v>30.09339357753862</v>
       </c>
       <c r="O20" t="n">
-        <v>5.491181442872702</v>
+        <v>5.485744578226243</v>
       </c>
       <c r="P20" t="n">
-        <v>352.4535087062669</v>
+        <v>352.4770136506503</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -35095,28 +35211,28 @@
         <v>0.0369</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6122022714558635</v>
+        <v>0.6095622241858325</v>
       </c>
       <c r="J21" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K21" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L21" t="n">
-        <v>0.365121400868206</v>
+        <v>0.3645028371682983</v>
       </c>
       <c r="M21" t="n">
-        <v>5.099383524114809</v>
+        <v>5.096867717601478</v>
       </c>
       <c r="N21" t="n">
-        <v>36.2293080675275</v>
+        <v>36.16506230717897</v>
       </c>
       <c r="O21" t="n">
-        <v>6.019078672648123</v>
+        <v>6.013739461198745</v>
       </c>
       <c r="P21" t="n">
-        <v>355.5083491411332</v>
+        <v>355.5361770740194</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -35173,28 +35289,28 @@
         <v>0.0313</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4999881360865202</v>
+        <v>0.4938456016622513</v>
       </c>
       <c r="J22" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K22" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1897562222562504</v>
+        <v>0.1863856807421469</v>
       </c>
       <c r="M22" t="n">
-        <v>6.611206651747881</v>
+        <v>6.624387621701676</v>
       </c>
       <c r="N22" t="n">
-        <v>59.34113451655787</v>
+        <v>59.43316304717774</v>
       </c>
       <c r="O22" t="n">
-        <v>7.703319707538943</v>
+        <v>7.70929069676178</v>
       </c>
       <c r="P22" t="n">
-        <v>353.0401333805091</v>
+        <v>353.1048799620005</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -35251,28 +35367,28 @@
         <v>0.0262</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9293971374875176</v>
+        <v>0.923446580524213</v>
       </c>
       <c r="J23" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K23" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L23" t="n">
-        <v>0.5169505287532343</v>
+        <v>0.5141173522763138</v>
       </c>
       <c r="M23" t="n">
-        <v>5.475429787846841</v>
+        <v>5.488320954454706</v>
       </c>
       <c r="N23" t="n">
-        <v>44.8706184870281</v>
+        <v>44.99177288773303</v>
       </c>
       <c r="O23" t="n">
-        <v>6.698553462280352</v>
+        <v>6.70759069172628</v>
       </c>
       <c r="P23" t="n">
-        <v>343.4682654448451</v>
+        <v>343.5309884504862</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -35329,28 +35445,28 @@
         <v>0.0362</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6349617273365084</v>
+        <v>0.6283159624511155</v>
       </c>
       <c r="J24" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K24" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L24" t="n">
-        <v>0.3890503373069419</v>
+        <v>0.3835938921517843</v>
       </c>
       <c r="M24" t="n">
-        <v>4.937361111730457</v>
+        <v>4.954335698323229</v>
       </c>
       <c r="N24" t="n">
-        <v>35.1974741150508</v>
+        <v>35.41537632275784</v>
       </c>
       <c r="O24" t="n">
-        <v>5.932745916946957</v>
+        <v>5.951081945558962</v>
       </c>
       <c r="P24" t="n">
-        <v>354.7033283531902</v>
+        <v>354.7733793334541</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -35407,28 +35523,28 @@
         <v>0.0481</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6598000829870979</v>
+        <v>0.6547695162420853</v>
       </c>
       <c r="J25" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K25" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L25" t="n">
-        <v>0.4179138080572175</v>
+        <v>0.4146292277287089</v>
       </c>
       <c r="M25" t="n">
-        <v>4.829172618821649</v>
+        <v>4.834064067746551</v>
       </c>
       <c r="N25" t="n">
-        <v>33.70870557260113</v>
+        <v>33.79002009256778</v>
       </c>
       <c r="O25" t="n">
-        <v>5.80591987307792</v>
+        <v>5.812918380002232</v>
       </c>
       <c r="P25" t="n">
-        <v>362.1253055078912</v>
+        <v>362.1783311772985</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -35485,28 +35601,28 @@
         <v>0.0572</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5541193018905179</v>
+        <v>0.5499989069829636</v>
       </c>
       <c r="J26" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K26" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L26" t="n">
-        <v>0.3623284018372673</v>
+        <v>0.3596183017999397</v>
       </c>
       <c r="M26" t="n">
-        <v>4.422020639389352</v>
+        <v>4.428188226084193</v>
       </c>
       <c r="N26" t="n">
-        <v>30.0412514146385</v>
+        <v>30.07192316768038</v>
       </c>
       <c r="O26" t="n">
-        <v>5.480990003150754</v>
+        <v>5.48378730146241</v>
       </c>
       <c r="P26" t="n">
-        <v>347.6615699895598</v>
+        <v>347.7050018152904</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -35563,28 +35679,28 @@
         <v>0.0602</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3696788152748224</v>
+        <v>0.3664369655185602</v>
       </c>
       <c r="J27" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K27" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L27" t="n">
-        <v>0.2269136434271091</v>
+        <v>0.224598536420854</v>
       </c>
       <c r="M27" t="n">
-        <v>4.005592308974248</v>
+        <v>4.010198326236892</v>
       </c>
       <c r="N27" t="n">
-        <v>25.88411345697865</v>
+        <v>25.8796664899211</v>
       </c>
       <c r="O27" t="n">
-        <v>5.087643212429371</v>
+        <v>5.087206157599778</v>
       </c>
       <c r="P27" t="n">
-        <v>345.4845373973989</v>
+        <v>345.5187087467035</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -35641,28 +35757,28 @@
         <v>0.0598</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2065552974570778</v>
+        <v>0.203538774419633</v>
       </c>
       <c r="J28" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K28" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L28" t="n">
-        <v>0.07939317310254168</v>
+        <v>0.07762164211197586</v>
       </c>
       <c r="M28" t="n">
-        <v>4.111489135604843</v>
+        <v>4.113222346775219</v>
       </c>
       <c r="N28" t="n">
-        <v>27.50302567829849</v>
+        <v>27.48280226425631</v>
       </c>
       <c r="O28" t="n">
-        <v>5.24433272002249</v>
+        <v>5.242404244643511</v>
       </c>
       <c r="P28" t="n">
-        <v>361.1364522414372</v>
+        <v>361.1682484905381</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -35719,28 +35835,28 @@
         <v>0.0559</v>
       </c>
       <c r="I29" t="n">
-        <v>0.07880128030286083</v>
+        <v>0.07564853043161196</v>
       </c>
       <c r="J29" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K29" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L29" t="n">
-        <v>0.01716956820876703</v>
+        <v>0.01590143860306503</v>
       </c>
       <c r="M29" t="n">
-        <v>3.40260448706091</v>
+        <v>3.408807842631355</v>
       </c>
       <c r="N29" t="n">
-        <v>19.76070963594502</v>
+        <v>19.77168106556341</v>
       </c>
       <c r="O29" t="n">
-        <v>4.44530197353847</v>
+        <v>4.446535850025659</v>
       </c>
       <c r="P29" t="n">
-        <v>372.5922706363685</v>
+        <v>372.6255028109665</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -35778,7 +35894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD311"/>
+  <dimension ref="A1:AD312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82661,6 +82777,158 @@
         </is>
       </c>
     </row>
+    <row r="312">
+      <c r="A312" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>-36.66821903748829,175.5578963747429</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>-36.66887569783532,175.55751826049385</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>-36.66951173488689,175.55706829569849</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>-36.670150274628654,175.55662707304404</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>-36.67083070806839,175.5563318674749</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>-36.67148552037159,175.5560302575494</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>-36.672161457018085,175.5557975889941</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>-36.6728665760884,175.55557920914038</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>-36.67357352286358,175.55536289618047</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>-36.6742876415169,175.55523886912644</t>
+        </is>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>-36.67500497481784,175.5551562547655</t>
+        </is>
+      </c>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>-36.6757208657409,175.55503847310368</t>
+        </is>
+      </c>
+      <c r="N312" t="inlineStr">
+        <is>
+          <t>-36.676440462677625,175.55496861052563</t>
+        </is>
+      </c>
+      <c r="O312" t="inlineStr">
+        <is>
+          <t>-36.677160155571094,175.55492530669898</t>
+        </is>
+      </c>
+      <c r="P312" t="inlineStr">
+        <is>
+          <t>-36.67788158740926,175.55491013154221</t>
+        </is>
+      </c>
+      <c r="Q312" t="inlineStr">
+        <is>
+          <t>-36.67859878412221,175.55492763506456</t>
+        </is>
+      </c>
+      <c r="R312" t="inlineStr">
+        <is>
+          <t>-36.67931693493268,175.55500346477618</t>
+        </is>
+      </c>
+      <c r="S312" t="inlineStr">
+        <is>
+          <t>-36.680032435852524,175.55510766531876</t>
+        </is>
+      </c>
+      <c r="T312" t="inlineStr">
+        <is>
+          <t>-36.68074237466294,175.55525848192158</t>
+        </is>
+      </c>
+      <c r="U312" t="inlineStr">
+        <is>
+          <t>-36.6814431431331,175.55543204672534</t>
+        </is>
+      </c>
+      <c r="V312" t="inlineStr">
+        <is>
+          <t>-36.68216264263473,175.55554522552868</t>
+        </is>
+      </c>
+      <c r="W312" t="inlineStr">
+        <is>
+          <t>-36.68285321920062,175.55580069134245</t>
+        </is>
+      </c>
+      <c r="X312" t="inlineStr">
+        <is>
+          <t>-36.683543665946054,175.55605669542194</t>
+        </is>
+      </c>
+      <c r="Y312" t="inlineStr">
+        <is>
+          <t>-36.68419605938221,175.55639230748548</t>
+        </is>
+      </c>
+      <c r="Z312" t="inlineStr">
+        <is>
+          <t>-36.68484646161071,175.5567607814239</t>
+        </is>
+      </c>
+      <c r="AA312" t="inlineStr">
+        <is>
+          <t>-36.68544943318977,175.55726005421477</t>
+        </is>
+      </c>
+      <c r="AB312" t="inlineStr">
+        <is>
+          <t>-36.685952541100555,175.55790851441085</t>
+        </is>
+      </c>
+      <c r="AC312" t="inlineStr">
+        <is>
+          <t>-36.68630176417363,175.55868121559445</t>
+        </is>
+      </c>
+      <c r="AD312" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0150/nzd0150.xlsx
+++ b/data/nzd0150/nzd0150.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD312"/>
+  <dimension ref="A1:AD313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30240,6 +30240,102 @@
       <c r="AD312" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:06:00+00:00</t>
+        </is>
+      </c>
+      <c r="B313" t="n">
+        <v>420.31</v>
+      </c>
+      <c r="C313" t="n">
+        <v>419.48</v>
+      </c>
+      <c r="D313" t="n">
+        <v>409.58</v>
+      </c>
+      <c r="E313" t="n">
+        <v>389.52</v>
+      </c>
+      <c r="F313" t="n">
+        <v>384.23</v>
+      </c>
+      <c r="G313" t="n">
+        <v>385.32</v>
+      </c>
+      <c r="H313" t="n">
+        <v>377.39</v>
+      </c>
+      <c r="I313" t="n">
+        <v>369.04</v>
+      </c>
+      <c r="J313" t="n">
+        <v>357.34</v>
+      </c>
+      <c r="K313" t="n">
+        <v>354.59</v>
+      </c>
+      <c r="L313" t="n">
+        <v>355.21</v>
+      </c>
+      <c r="M313" t="n">
+        <v>354.09</v>
+      </c>
+      <c r="N313" t="n">
+        <v>353.78</v>
+      </c>
+      <c r="O313" t="n">
+        <v>356.47</v>
+      </c>
+      <c r="P313" t="n">
+        <v>360.94</v>
+      </c>
+      <c r="Q313" t="n">
+        <v>363.01</v>
+      </c>
+      <c r="R313" t="n">
+        <v>359.87</v>
+      </c>
+      <c r="S313" t="n">
+        <v>361.29</v>
+      </c>
+      <c r="T313" t="n">
+        <v>363.07</v>
+      </c>
+      <c r="U313" t="n">
+        <v>364.98</v>
+      </c>
+      <c r="V313" t="n">
+        <v>350.26</v>
+      </c>
+      <c r="W313" t="n">
+        <v>358.3</v>
+      </c>
+      <c r="X313" t="n">
+        <v>362.01</v>
+      </c>
+      <c r="Y313" t="n">
+        <v>372.39</v>
+      </c>
+      <c r="Z313" t="n">
+        <v>356.16</v>
+      </c>
+      <c r="AA313" t="n">
+        <v>348.93</v>
+      </c>
+      <c r="AB313" t="n">
+        <v>360.41</v>
+      </c>
+      <c r="AC313" t="n">
+        <v>370.12</v>
+      </c>
+      <c r="AD313" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -30254,7 +30350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B330"/>
+  <dimension ref="A1:B331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33557,6 +33653,16 @@
       </c>
       <c r="B330" t="n">
         <v>0.12</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B331" t="n">
+        <v>0.83</v>
       </c>
     </row>
   </sheetData>
@@ -33725,28 +33831,28 @@
         <v>0.0104</v>
       </c>
       <c r="I2" t="n">
-        <v>-6.743962223297467</v>
+        <v>-6.712584824072106</v>
       </c>
       <c r="J2" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K2" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7665002540512934</v>
+        <v>0.7645841482571232</v>
       </c>
       <c r="M2" t="n">
-        <v>19.88720238449401</v>
+        <v>19.96793221700814</v>
       </c>
       <c r="N2" t="n">
-        <v>706.8485830688849</v>
+        <v>710.8360956138958</v>
       </c>
       <c r="O2" t="n">
-        <v>26.58662413825578</v>
+        <v>26.66150962743663</v>
       </c>
       <c r="P2" t="n">
-        <v>558.4779741907277</v>
+        <v>558.1189395447932</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -33807,28 +33913,28 @@
         <v>0.0103</v>
       </c>
       <c r="I3" t="n">
-        <v>-3.6558835416393</v>
+        <v>-3.634343268364161</v>
       </c>
       <c r="J3" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K3" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4939825053221673</v>
+        <v>0.4918617403079151</v>
       </c>
       <c r="M3" t="n">
-        <v>21.94303140834575</v>
+        <v>21.96031104291098</v>
       </c>
       <c r="N3" t="n">
-        <v>763.3900843741026</v>
+        <v>764.1252513344225</v>
       </c>
       <c r="O3" t="n">
-        <v>27.62951473287402</v>
+        <v>27.64281554643851</v>
       </c>
       <c r="P3" t="n">
-        <v>486.3637816235265</v>
+        <v>486.133364653962</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33885,28 +33991,28 @@
         <v>0.0125</v>
       </c>
       <c r="I4" t="n">
-        <v>2.034766937053583</v>
+        <v>2.030508029554777</v>
       </c>
       <c r="J4" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K4" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1585852747948256</v>
+        <v>0.1590337375998034</v>
       </c>
       <c r="M4" t="n">
-        <v>29.3780778932007</v>
+        <v>29.29613858798297</v>
       </c>
       <c r="N4" t="n">
-        <v>1233.402822215884</v>
+        <v>1229.177571306847</v>
       </c>
       <c r="O4" t="n">
-        <v>35.11983516783476</v>
+        <v>35.05962879590779</v>
       </c>
       <c r="P4" t="n">
-        <v>361.0275560673739</v>
+        <v>361.0734037893218</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33963,28 +34069,28 @@
         <v>0.0224</v>
       </c>
       <c r="I5" t="n">
-        <v>1.641634496889772</v>
+        <v>1.63578990721029</v>
       </c>
       <c r="J5" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K5" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5192664560727099</v>
+        <v>0.5189269402592395</v>
       </c>
       <c r="M5" t="n">
-        <v>9.268482251354747</v>
+        <v>9.265334086481557</v>
       </c>
       <c r="N5" t="n">
-        <v>135.8134887813925</v>
+        <v>135.6164195948935</v>
       </c>
       <c r="O5" t="n">
-        <v>11.65390444363572</v>
+        <v>11.64544630295007</v>
       </c>
       <c r="P5" t="n">
-        <v>354.0935502299918</v>
+        <v>354.1566217920936</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34041,28 +34147,28 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6989700936593111</v>
+        <v>0.6999596859721009</v>
       </c>
       <c r="J6" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K6" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4181676637551964</v>
+        <v>0.4206543065706759</v>
       </c>
       <c r="M6" t="n">
-        <v>3.128081115541741</v>
+        <v>3.123483677040904</v>
       </c>
       <c r="N6" t="n">
-        <v>36.76826711324419</v>
+        <v>36.65627397772403</v>
       </c>
       <c r="O6" t="n">
-        <v>6.063684285419566</v>
+        <v>6.054442499332538</v>
       </c>
       <c r="P6" t="n">
-        <v>363.9515695139794</v>
+        <v>363.9408560093038</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34119,28 +34225,28 @@
         <v>0.0726</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2401739453947424</v>
+        <v>0.2414855732404129</v>
       </c>
       <c r="J7" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K7" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03039575205754375</v>
+        <v>0.03093858008278305</v>
       </c>
       <c r="M7" t="n">
-        <v>4.136464163675124</v>
+        <v>4.127216404846002</v>
       </c>
       <c r="N7" t="n">
-        <v>101.1705395093069</v>
+        <v>100.8557555938267</v>
       </c>
       <c r="O7" t="n">
-        <v>10.05835670024219</v>
+        <v>10.04269662958245</v>
       </c>
       <c r="P7" t="n">
-        <v>376.8760681235476</v>
+        <v>376.8619964496796</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34197,28 +34303,28 @@
         <v>0.0303</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0399861588748625</v>
+        <v>0.04219477134447296</v>
       </c>
       <c r="J8" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K8" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001064440912879383</v>
+        <v>0.001193501197047753</v>
       </c>
       <c r="M8" t="n">
-        <v>5.904895913559741</v>
+        <v>5.894264157931146</v>
       </c>
       <c r="N8" t="n">
-        <v>82.9512209872285</v>
+        <v>82.71970207081742</v>
       </c>
       <c r="O8" t="n">
-        <v>9.107756089577085</v>
+        <v>9.095037222068825</v>
       </c>
       <c r="P8" t="n">
-        <v>372.9568456052849</v>
+        <v>372.9332589396825</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34275,28 +34381,28 @@
         <v>0.0271</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.05346991596587025</v>
+        <v>-0.05359029676233704</v>
       </c>
       <c r="J9" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K9" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001236940099117123</v>
+        <v>0.001251839949681366</v>
       </c>
       <c r="M9" t="n">
-        <v>7.81038580497558</v>
+        <v>7.785623015774254</v>
       </c>
       <c r="N9" t="n">
-        <v>128.4315167099088</v>
+        <v>128.0146389320585</v>
       </c>
       <c r="O9" t="n">
-        <v>11.33276297775211</v>
+        <v>11.31435543599628</v>
       </c>
       <c r="P9" t="n">
-        <v>370.6582442630078</v>
+        <v>370.6595256135943</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34353,28 +34459,28 @@
         <v>0.0339</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3779145910432393</v>
+        <v>-0.3770701826312555</v>
       </c>
       <c r="J10" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K10" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L10" t="n">
-        <v>0.05704830561629215</v>
+        <v>0.0572110462137656</v>
       </c>
       <c r="M10" t="n">
-        <v>8.104352050312432</v>
+        <v>8.0826609788895</v>
       </c>
       <c r="N10" t="n">
-        <v>129.0396338822534</v>
+        <v>128.6285522263327</v>
       </c>
       <c r="O10" t="n">
-        <v>11.35956134198207</v>
+        <v>11.34145282696766</v>
       </c>
       <c r="P10" t="n">
-        <v>366.2301805149739</v>
+        <v>366.221105556433</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -34431,28 +34537,28 @@
         <v>0.0553</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.04008778788009808</v>
+        <v>-0.03986768586095382</v>
       </c>
       <c r="J11" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K11" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L11" t="n">
-        <v>0.001036180971406564</v>
+        <v>0.001032609973444565</v>
       </c>
       <c r="M11" t="n">
-        <v>6.06241342008477</v>
+        <v>6.044080346059251</v>
       </c>
       <c r="N11" t="n">
-        <v>83.80509932810344</v>
+        <v>83.53335167520196</v>
       </c>
       <c r="O11" t="n">
-        <v>9.154512511767267</v>
+        <v>9.139658181529654</v>
       </c>
       <c r="P11" t="n">
-        <v>355.3406187359233</v>
+        <v>355.3382323782428</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -34509,28 +34615,28 @@
         <v>0.0609</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1019186266648813</v>
+        <v>0.1024958903533583</v>
       </c>
       <c r="J12" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K12" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01797139120260971</v>
+        <v>0.01830399375975988</v>
       </c>
       <c r="M12" t="n">
-        <v>4.303365870966604</v>
+        <v>4.292605458593367</v>
       </c>
       <c r="N12" t="n">
-        <v>31.68764708560627</v>
+        <v>31.58857916486047</v>
       </c>
       <c r="O12" t="n">
-        <v>5.629178189185901</v>
+        <v>5.620371799521849</v>
       </c>
       <c r="P12" t="n">
-        <v>351.5787095907391</v>
+        <v>351.5725975078901</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -34587,28 +34693,28 @@
         <v>0.061</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1816656010621808</v>
+        <v>0.1819892346521269</v>
       </c>
       <c r="J13" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K13" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L13" t="n">
-        <v>0.08298550605482524</v>
+        <v>0.0838249891666063</v>
       </c>
       <c r="M13" t="n">
-        <v>3.458211007307625</v>
+        <v>3.448878120530349</v>
       </c>
       <c r="N13" t="n">
-        <v>20.35915637542257</v>
+        <v>20.29468688937904</v>
       </c>
       <c r="O13" t="n">
-        <v>4.512112185598068</v>
+        <v>4.504962473692655</v>
       </c>
       <c r="P13" t="n">
-        <v>348.7075104785314</v>
+        <v>348.7040838377191</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -34665,28 +34771,28 @@
         <v>0.0796</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1340995401170645</v>
+        <v>0.1346932884313139</v>
       </c>
       <c r="J14" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K14" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L14" t="n">
-        <v>0.04667338685617028</v>
+        <v>0.04739801332179572</v>
       </c>
       <c r="M14" t="n">
-        <v>3.598450327459683</v>
+        <v>3.589731856244678</v>
       </c>
       <c r="N14" t="n">
-        <v>20.50536017130922</v>
+        <v>20.44227744818591</v>
       </c>
       <c r="O14" t="n">
-        <v>4.528284462278095</v>
+        <v>4.521313686107822</v>
       </c>
       <c r="P14" t="n">
-        <v>349.2598207365396</v>
+        <v>349.2535341140471</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -34743,28 +34849,28 @@
         <v>0.108</v>
       </c>
       <c r="I15" t="n">
-        <v>0.256392489754112</v>
+        <v>0.2563433133941789</v>
       </c>
       <c r="J15" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K15" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1634988040752771</v>
+        <v>0.1644687785369862</v>
       </c>
       <c r="M15" t="n">
-        <v>3.430676176336618</v>
+        <v>3.419912375983476</v>
       </c>
       <c r="N15" t="n">
-        <v>18.7759971157253</v>
+        <v>18.71583574467138</v>
       </c>
       <c r="O15" t="n">
-        <v>4.333127867456176</v>
+        <v>4.326180271864706</v>
       </c>
       <c r="P15" t="n">
-        <v>349.6464661383689</v>
+        <v>349.6469868189385</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -34821,28 +34927,28 @@
         <v>0.2</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3269974056231663</v>
+        <v>0.3272770894082561</v>
       </c>
       <c r="J16" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K16" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2325465970861795</v>
+        <v>0.2341817835167347</v>
       </c>
       <c r="M16" t="n">
-        <v>3.266995014156294</v>
+        <v>3.257748352497584</v>
       </c>
       <c r="N16" t="n">
-        <v>19.70021954124911</v>
+        <v>19.63766349879446</v>
       </c>
       <c r="O16" t="n">
-        <v>4.438492935811559</v>
+        <v>4.431440341333104</v>
       </c>
       <c r="P16" t="n">
-        <v>351.7171054612846</v>
+        <v>351.7141441621416</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -34899,28 +35005,28 @@
         <v>0.057</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4362120372486998</v>
+        <v>0.4362733359452255</v>
       </c>
       <c r="J17" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K17" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3526774409605975</v>
+        <v>0.3544463472372318</v>
       </c>
       <c r="M17" t="n">
-        <v>3.348890746246294</v>
+        <v>3.338476234229236</v>
       </c>
       <c r="N17" t="n">
-        <v>19.49749320175451</v>
+        <v>19.43502937048659</v>
       </c>
       <c r="O17" t="n">
-        <v>4.415596585032934</v>
+        <v>4.408517820139394</v>
       </c>
       <c r="P17" t="n">
-        <v>351.1821678528755</v>
+        <v>351.1815188206929</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -34977,28 +35083,28 @@
         <v>0.0491</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5331488833381224</v>
+        <v>0.5324404973901321</v>
       </c>
       <c r="J18" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K18" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L18" t="n">
-        <v>0.4362574302764544</v>
+        <v>0.4373932496435436</v>
       </c>
       <c r="M18" t="n">
-        <v>3.601181836361675</v>
+        <v>3.593145242078294</v>
       </c>
       <c r="N18" t="n">
-        <v>20.50573905281087</v>
+        <v>20.44377278603789</v>
       </c>
       <c r="O18" t="n">
-        <v>4.5283262970783</v>
+        <v>4.521479048501484</v>
       </c>
       <c r="P18" t="n">
-        <v>346.6135862842142</v>
+        <v>346.6210866929348</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -35055,28 +35161,28 @@
         <v>0.0369</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5549669894431261</v>
+        <v>0.5542174804290233</v>
       </c>
       <c r="J19" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K19" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4043837750260082</v>
+        <v>0.405489889452129</v>
       </c>
       <c r="M19" t="n">
-        <v>4.065141623178593</v>
+        <v>4.056129610954781</v>
       </c>
       <c r="N19" t="n">
-        <v>25.32488748370011</v>
+        <v>25.24792412114124</v>
       </c>
       <c r="O19" t="n">
-        <v>5.032383876822207</v>
+        <v>5.024731248648155</v>
       </c>
       <c r="P19" t="n">
-        <v>347.515941950959</v>
+        <v>347.5238777717662</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -35133,28 +35239,28 @@
         <v>0.0413</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5709410775428457</v>
+        <v>0.5678391475334071</v>
       </c>
       <c r="J20" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K20" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3768369794106136</v>
+        <v>0.3754678358837252</v>
       </c>
       <c r="M20" t="n">
-        <v>4.466438765298427</v>
+        <v>4.46909809469105</v>
       </c>
       <c r="N20" t="n">
-        <v>30.09339357753862</v>
+        <v>30.06898390580535</v>
       </c>
       <c r="O20" t="n">
-        <v>5.485744578226243</v>
+        <v>5.483519299300892</v>
       </c>
       <c r="P20" t="n">
-        <v>352.4770136506503</v>
+        <v>352.509856965738</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -35211,28 +35317,28 @@
         <v>0.0369</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6095622241858325</v>
+        <v>0.6050390081034955</v>
       </c>
       <c r="J21" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K21" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L21" t="n">
-        <v>0.3645028371682983</v>
+        <v>0.3618023416059963</v>
       </c>
       <c r="M21" t="n">
-        <v>5.096867717601478</v>
+        <v>5.104016738432114</v>
       </c>
       <c r="N21" t="n">
-        <v>36.16506230717897</v>
+        <v>36.20233693390641</v>
       </c>
       <c r="O21" t="n">
-        <v>6.013739461198745</v>
+        <v>6.016837785241215</v>
       </c>
       <c r="P21" t="n">
-        <v>355.5361770740194</v>
+        <v>355.5840690027703</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -35289,28 +35395,28 @@
         <v>0.0313</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4938456016622513</v>
+        <v>0.4833513361983512</v>
       </c>
       <c r="J22" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K22" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1863856807421469</v>
+        <v>0.1790217254784783</v>
       </c>
       <c r="M22" t="n">
-        <v>6.624387621701676</v>
+        <v>6.661288602222947</v>
       </c>
       <c r="N22" t="n">
-        <v>59.43316304717774</v>
+        <v>60.06725629232595</v>
       </c>
       <c r="O22" t="n">
-        <v>7.70929069676178</v>
+        <v>7.750306851494717</v>
       </c>
       <c r="P22" t="n">
-        <v>353.1048799620005</v>
+        <v>353.2159935158835</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -35367,28 +35473,28 @@
         <v>0.0262</v>
       </c>
       <c r="I23" t="n">
-        <v>0.923446580524213</v>
+        <v>0.9168910846871238</v>
       </c>
       <c r="J23" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K23" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L23" t="n">
-        <v>0.5141173522763138</v>
+        <v>0.510635082267419</v>
       </c>
       <c r="M23" t="n">
-        <v>5.488320954454706</v>
+        <v>5.504990138065458</v>
       </c>
       <c r="N23" t="n">
-        <v>44.99177288773303</v>
+        <v>45.16933584489511</v>
       </c>
       <c r="O23" t="n">
-        <v>6.70759069172628</v>
+        <v>6.720813629680197</v>
       </c>
       <c r="P23" t="n">
-        <v>343.5309884504862</v>
+        <v>343.6003982097904</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -35445,28 +35551,28 @@
         <v>0.0362</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6283159624511155</v>
+        <v>0.6220280570040934</v>
       </c>
       <c r="J24" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K24" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L24" t="n">
-        <v>0.3835938921517843</v>
+        <v>0.378639126672616</v>
       </c>
       <c r="M24" t="n">
-        <v>4.954335698323229</v>
+        <v>4.969173712525849</v>
       </c>
       <c r="N24" t="n">
-        <v>35.41537632275784</v>
+        <v>35.59790038975169</v>
       </c>
       <c r="O24" t="n">
-        <v>5.951081945558962</v>
+        <v>5.966397605737627</v>
       </c>
       <c r="P24" t="n">
-        <v>354.7733793334541</v>
+        <v>354.8399558387942</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -35523,28 +35629,28 @@
         <v>0.0481</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6547695162420853</v>
+        <v>0.6499559970542981</v>
       </c>
       <c r="J25" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K25" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L25" t="n">
-        <v>0.4146292277287089</v>
+        <v>0.4116144029466332</v>
       </c>
       <c r="M25" t="n">
-        <v>4.834064067746551</v>
+        <v>4.837853199796478</v>
       </c>
       <c r="N25" t="n">
-        <v>33.79002009256778</v>
+        <v>33.85520149963509</v>
       </c>
       <c r="O25" t="n">
-        <v>5.812918380002232</v>
+        <v>5.818522278004536</v>
       </c>
       <c r="P25" t="n">
-        <v>362.1783311772985</v>
+        <v>362.2292968428306</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -35601,28 +35707,28 @@
         <v>0.0572</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5499989069829636</v>
+        <v>0.5458733995662816</v>
       </c>
       <c r="J26" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K26" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L26" t="n">
-        <v>0.3596183017999397</v>
+        <v>0.3568960148892885</v>
       </c>
       <c r="M26" t="n">
-        <v>4.428188226084193</v>
+        <v>4.434178692349865</v>
       </c>
       <c r="N26" t="n">
-        <v>30.07192316768038</v>
+        <v>30.10297289276321</v>
       </c>
       <c r="O26" t="n">
-        <v>5.48378730146241</v>
+        <v>5.48661761860285</v>
       </c>
       <c r="P26" t="n">
-        <v>347.7050018152904</v>
+        <v>347.7486827944132</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -35679,28 +35785,28 @@
         <v>0.0602</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3664369655185602</v>
+        <v>0.3622450373298736</v>
       </c>
       <c r="J27" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K27" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L27" t="n">
-        <v>0.224598536420854</v>
+        <v>0.2210246697760381</v>
       </c>
       <c r="M27" t="n">
-        <v>4.010198326236892</v>
+        <v>4.019731260513866</v>
       </c>
       <c r="N27" t="n">
-        <v>25.8796664899211</v>
+        <v>25.92828935159034</v>
       </c>
       <c r="O27" t="n">
-        <v>5.087206157599778</v>
+        <v>5.091982850677164</v>
       </c>
       <c r="P27" t="n">
-        <v>345.5187087467035</v>
+        <v>345.5630929906764</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -35757,28 +35863,28 @@
         <v>0.0598</v>
       </c>
       <c r="I28" t="n">
-        <v>0.203538774419633</v>
+        <v>0.199484732333872</v>
       </c>
       <c r="J28" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K28" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L28" t="n">
-        <v>0.07762164211197586</v>
+        <v>0.0749956107212657</v>
       </c>
       <c r="M28" t="n">
-        <v>4.113222346775219</v>
+        <v>4.120247511861169</v>
       </c>
       <c r="N28" t="n">
-        <v>27.48280226425631</v>
+        <v>27.51777366400907</v>
       </c>
       <c r="O28" t="n">
-        <v>5.242404244643511</v>
+        <v>5.24573861949002</v>
       </c>
       <c r="P28" t="n">
-        <v>361.1682484905381</v>
+        <v>361.2111727928906</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -35835,28 +35941,28 @@
         <v>0.0559</v>
       </c>
       <c r="I29" t="n">
-        <v>0.07564853043161196</v>
+        <v>0.07269237521551829</v>
       </c>
       <c r="J29" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K29" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L29" t="n">
-        <v>0.01590143860306503</v>
+        <v>0.01476102351054631</v>
       </c>
       <c r="M29" t="n">
-        <v>3.408807842631355</v>
+        <v>3.413813064091665</v>
       </c>
       <c r="N29" t="n">
-        <v>19.77168106556341</v>
+        <v>19.77374156425649</v>
       </c>
       <c r="O29" t="n">
-        <v>4.446535850025659</v>
+        <v>4.446767541063563</v>
       </c>
       <c r="P29" t="n">
-        <v>372.6255028109665</v>
+        <v>372.6568026587756</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -35894,7 +36000,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD312"/>
+  <dimension ref="A1:AD313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82929,6 +83035,158 @@
         </is>
       </c>
     </row>
+    <row r="313">
+      <c r="A313" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:06:00+00:00</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>-36.66824730248923,175.55799487668816</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>-36.66891913854251,175.55766964918587</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>-36.66956354979891,175.5572488678217</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>-36.67017724042676,175.5567210470651</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>-36.670835575241455,175.55634882929135</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>-36.67148948150165,175.55605093003197</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>-36.67216526775818,175.55584027391953</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>-36.67287172832346,175.5556454460084</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>-36.67357743689655,175.55541321439395</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>-36.67429088879967,175.55528061581816</t>
+        </is>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>-36.67500725225037,175.55518553338464</t>
+        </is>
+      </c>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>-36.675722973718294,175.5550708022454</t>
+        </is>
+      </c>
+      <c r="N313" t="inlineStr">
+        <is>
+          <t>-36.67644171565454,175.55499283109629</t>
+        </is>
+      </c>
+      <c r="O313" t="inlineStr">
+        <is>
+          <t>-36.67716144303187,175.55495064549962</t>
+        </is>
+      </c>
+      <c r="P313" t="inlineStr">
+        <is>
+          <t>-36.67788191099059,175.55492791076887</t>
+        </is>
+      </c>
+      <c r="Q313" t="inlineStr">
+        <is>
+          <t>-36.6785974437129,175.5549506157047</t>
+        </is>
+      </c>
+      <c r="R313" t="inlineStr">
+        <is>
+          <t>-36.6793159586189,175.5550130071711</t>
+        </is>
+      </c>
+      <c r="S313" t="inlineStr">
+        <is>
+          <t>-36.68003049456048,175.5551266393226</t>
+        </is>
+      </c>
+      <c r="T313" t="inlineStr">
+        <is>
+          <t>-36.68074411896929,175.55524399026928</t>
+        </is>
+      </c>
+      <c r="U313" t="inlineStr">
+        <is>
+          <t>-36.681448907894485,175.55540063830549</t>
+        </is>
+      </c>
+      <c r="V313" t="inlineStr">
+        <is>
+          <t>-36.68217928267286,175.5554727221025</t>
+        </is>
+      </c>
+      <c r="W313" t="inlineStr">
+        <is>
+          <t>-36.68285551524909,175.55579068708045</t>
+        </is>
+      </c>
+      <c r="X313" t="inlineStr">
+        <is>
+          <t>-36.68354243150192,175.5560620741013</t>
+        </is>
+      </c>
+      <c r="Y313" t="inlineStr">
+        <is>
+          <t>-36.6841948199609,175.55639541487352</t>
+        </is>
+      </c>
+      <c r="Z313" t="inlineStr">
+        <is>
+          <t>-36.68484657192883,175.5567606045418</t>
+        </is>
+      </c>
+      <c r="AA313" t="inlineStr">
+        <is>
+          <t>-36.68545776049921,175.5572471248579</t>
+        </is>
+      </c>
+      <c r="AB313" t="inlineStr">
+        <is>
+          <t>-36.685963319082596,175.5578961305235</t>
+        </is>
+      </c>
+      <c r="AC313" t="inlineStr">
+        <is>
+          <t>-36.68629982458268,175.5586828461833</t>
+        </is>
+      </c>
+      <c r="AD313" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
